--- a/Shared/XLS/Consumable.xlsx
+++ b/Shared/XLS/Consumable.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>!Table</t>
   </si>
@@ -48,14 +48,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SkillPoint</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -72,22 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>CooldownGroup</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooldown</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>!string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -100,27 +76,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Item_HealSmall</t>
-  </si>
-  <si>
     <t>SkillPoint_Item</t>
   </si>
   <si>
-    <t>Skill_Item_HealLarge</t>
-  </si>
-  <si>
-    <t>Skill_Item_AtkBuff</t>
-  </si>
-  <si>
-    <t>스킬 사용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬포인트 획득</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 보상</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +558,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -607,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -625,7 +584,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C1" s="8"/>
     </row>
@@ -634,28 +593,12 @@
         <v>4</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -666,7 +609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -674,164 +617,74 @@
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
       <c r="B4">
-        <v>1030100001</v>
+        <v>1030300001</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>1030100002</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>1030100003</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>1030200001</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>1030200002</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>1001</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9">
-        <v>1030300001</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
